--- a/output/Tables/Scenarios/HIA_scenarios.xlsx
+++ b/output/Tables/Scenarios/HIA_scenarios.xlsx
@@ -438,40 +438,40 @@
         </is>
       </c>
       <c r="B2">
-        <v>276215.276</v>
+        <v>238471.472</v>
       </c>
       <c r="C2">
-        <v>264254.083</v>
+        <v>227717.451</v>
       </c>
       <c r="D2">
-        <v>288334.913</v>
+        <v>249296.46</v>
       </c>
       <c r="E2">
-        <v>764692.493</v>
+        <v>676266.176</v>
       </c>
       <c r="F2">
-        <v>738967.635</v>
+        <v>652862.1139999999</v>
       </c>
       <c r="G2">
-        <v>790752.768</v>
+        <v>699687.081</v>
       </c>
       <c r="H2">
-        <v>3414882302.14</v>
+        <v>2518460749.073</v>
       </c>
       <c r="I2">
-        <v>3258736761.879</v>
+        <v>2394558879.829</v>
       </c>
       <c r="J2">
-        <v>3573276711.887</v>
+        <v>2643981882.813</v>
       </c>
       <c r="K2">
-        <v>101706015831.241</v>
+        <v>89941034959.235</v>
       </c>
       <c r="L2">
-        <v>98265373980.851</v>
+        <v>86825312368.58897</v>
       </c>
       <c r="M2">
-        <v>105168690068.69</v>
+        <v>93063290278.25801</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
@@ -486,40 +486,40 @@
         </is>
       </c>
       <c r="B3">
-        <v>1025387.215</v>
+        <v>839180.532</v>
       </c>
       <c r="C3">
-        <v>1003435.219</v>
+        <v>821764.648</v>
       </c>
       <c r="D3">
-        <v>1047442.638</v>
+        <v>856584.2830000001</v>
       </c>
       <c r="E3">
-        <v>2277977.125</v>
+        <v>2087399.422</v>
       </c>
       <c r="F3">
-        <v>2236378.145</v>
+        <v>2051898.283</v>
       </c>
       <c r="G3">
-        <v>2319970.947</v>
+        <v>2123080.487</v>
       </c>
       <c r="H3">
-        <v>13000395825.457</v>
+        <v>9519006379.667</v>
       </c>
       <c r="I3">
-        <v>12689883487.339</v>
+        <v>9292733043.577999</v>
       </c>
       <c r="J3">
-        <v>13314821064.444</v>
+        <v>9747453818.237</v>
       </c>
       <c r="K3">
-        <v>302974325767.796</v>
+        <v>277629291972.888</v>
       </c>
       <c r="L3">
-        <v>297413048988.73</v>
+        <v>272884047077.203</v>
       </c>
       <c r="M3">
-        <v>308547875002.449</v>
+        <v>282372909238.896</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
@@ -534,40 +534,40 @@
         </is>
       </c>
       <c r="B4">
-        <v>345005.58</v>
+        <v>309589.341</v>
       </c>
       <c r="C4">
-        <v>330884.732</v>
+        <v>296684.289</v>
       </c>
       <c r="D4">
-        <v>359385.669</v>
+        <v>322617.838</v>
       </c>
       <c r="E4">
-        <v>922703.7050000001</v>
+        <v>842047.1349999999</v>
       </c>
       <c r="F4">
-        <v>893364.848</v>
+        <v>815275.849</v>
       </c>
       <c r="G4">
-        <v>952550.3429999999</v>
+        <v>869027.3150000001</v>
       </c>
       <c r="H4">
-        <v>4279917804.558</v>
+        <v>3298308826.819</v>
       </c>
       <c r="I4">
-        <v>4095447030.794</v>
+        <v>3150944061.415</v>
       </c>
       <c r="J4">
-        <v>4468322005.476</v>
+        <v>3448890885.023</v>
       </c>
       <c r="K4">
-        <v>122720349655.447</v>
+        <v>111991743474.312</v>
       </c>
       <c r="L4">
-        <v>118808174355.626</v>
+        <v>108432705922.633</v>
       </c>
       <c r="M4">
-        <v>126691546976.211</v>
+        <v>115585023661.381</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -582,40 +582,40 @@
         </is>
       </c>
       <c r="B5">
-        <v>469230.3959999999</v>
+        <v>416416.117</v>
       </c>
       <c r="C5">
-        <v>443594.0599999999</v>
+        <v>393478.651</v>
       </c>
       <c r="D5">
-        <v>495019.531</v>
+        <v>439464.312</v>
       </c>
       <c r="E5">
-        <v>1360769.854</v>
+        <v>1298874.412999999</v>
       </c>
       <c r="F5">
-        <v>1302804.038</v>
+        <v>1244105.866</v>
       </c>
       <c r="G5">
-        <v>1419177.977</v>
+        <v>1353822.357</v>
       </c>
       <c r="H5">
-        <v>5719630979.415</v>
+        <v>4691109390.636002</v>
       </c>
       <c r="I5">
-        <v>5401166550.584999</v>
+        <v>4422056701.443999</v>
       </c>
       <c r="J5">
-        <v>6042086448.152999</v>
+        <v>4963903796.731001</v>
       </c>
       <c r="K5">
-        <v>180989084746.239</v>
+        <v>172758253851.587</v>
       </c>
       <c r="L5">
-        <v>173269368266.2661</v>
+        <v>165455283367.192</v>
       </c>
       <c r="M5">
-        <v>188790744292.316</v>
+        <v>180099058762.698</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
